--- a/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-05_Accounting_Disbursement_ACSL_Vol2_v1.0.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/TestPlans/BIBS_TestPlan_BRD-05_Accounting_Disbursement_ACSL_Vol2_v1.0.xlsx
@@ -1286,7 +1286,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>The FRS names the checker "Marketing / Comptrollership" without the permission that allows posting a liquidation; testers cannot tell which demo user checks.</t>
+          <t>The FRS names the checker "Marketing / Comptrollership" without the permission that allows posting a liquidation; testers cannot tell which SIT/UAT user checks.</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>The demo data has one ACSL processor (acsl); re-assigning a correction to "acslproc2" (acceptance criterion) needs a second processor that the demo does not provide.</t>
+          <t>The seed data has one ACSL processor (acsl); re-assigning a correction to "acslproc2" (acceptance criterion) needs a second processor that the seed does not provide.</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Add a second ACSL processor to the demo users or change the criterion.</t>
+          <t>Add a second ACSL processor to the SIT/UAT users or change the criterion.</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Role code and name (and demo user for built BRDs)</t>
+          <t>Role code and name (and SIT/UAT user for built BRDs)</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr"/>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Demo seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
+          <t>Seed that provides it (built BRDs) or how to prepare it; non-production data is masked</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-DPA-01 Demo users and roles</t>
+          <t>Data: TD-DPA-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
-          <t>CollectionsAccountingFoundationIT#demoPersonasHoldTheirPermissions</t>
+          <t>CollectionsAccountingFoundationIT#seedPersonasHoldTheirPermissions</t>
         </is>
       </c>
       <c r="N5" s="27" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-DPA-01 Demo users and roles</t>
+          <t>Data: TD-DPA-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-DPA-01 Demo users and roles</t>
+          <t>Data: TD-DPA-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J7" s="12" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>Data: TD-DPA-01 Demo users and roles</t>
+          <t>Data: TD-DPA-01 SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H11" s="12" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H24" s="12" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>PRQ_APPROVER – Marketing Approver (demo user mktappr)</t>
+          <t>PRQ_APPROVER – Marketing Approver (SIT/UAT user mktappr)</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H34" s="12" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="M38" s="12" t="inlineStr">
         <is>
-          <t>DisbursementDemoIT#theStorylineCoversEveryDisbursementScreen; labels.test.ts#validates the encode form</t>
+          <t>DisbursementSeedIT#theStorylineCoversEveryDisbursementScreen; labels.test.ts#validates the encode form</t>
         </is>
       </c>
       <c r="N38" s="27" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
@@ -12443,7 +12443,7 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -12735,7 +12735,7 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H50" s="12" t="inlineStr">
@@ -13030,7 +13030,7 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="M51" s="12" t="inlineStr">
         <is>
-          <t>DisbursementDemoIT#theStorylineCoversEveryDisbursementScreen</t>
+          <t>DisbursementSeedIT#theStorylineCoversEveryDisbursementScreen</t>
         </is>
       </c>
       <c r="N51" s="27" t="inlineStr">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H53" s="12" t="inlineStr">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H55" s="12" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H56" s="12" t="inlineStr">
@@ -13459,7 +13459,7 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H58" s="12" t="inlineStr">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H59" s="12" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H60" s="12" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H61" s="12" t="inlineStr">
@@ -13810,7 +13810,7 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H62" s="12" t="inlineStr">
@@ -13879,7 +13879,7 @@
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H64" s="12" t="inlineStr">
@@ -14020,7 +14020,7 @@
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H65" s="12" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H66" s="12" t="inlineStr">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H67" s="12" t="inlineStr">
@@ -14233,7 +14233,7 @@
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H68" s="12" t="inlineStr">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>FIN_ADMIN – Comptrollership administrator (demo user fmanager, badmin)</t>
+          <t>FIN_ADMIN – Comptrollership administrator (SIT/UAT user fmanager, badmin)</t>
         </is>
       </c>
       <c r="H69" s="12" t="inlineStr">
@@ -14378,7 +14378,7 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>FIN_ADMIN – Comptrollership administrator (demo user fmanager, badmin)</t>
+          <t>FIN_ADMIN – Comptrollership administrator (SIT/UAT user fmanager, badmin)</t>
         </is>
       </c>
       <c r="H70" s="12" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>FIN_ADMIN – Comptrollership administrator (demo user fmanager, badmin)</t>
+          <t>FIN_ADMIN – Comptrollership administrator (SIT/UAT user fmanager, badmin)</t>
         </is>
       </c>
       <c r="H71" s="12" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>FIN_ADMIN – Comptrollership administrator (demo user fmanager, badmin)</t>
+          <t>FIN_ADMIN – Comptrollership administrator (SIT/UAT user fmanager, badmin)</t>
         </is>
       </c>
       <c r="H72" s="12" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>FIN_ADMIN – Comptrollership administrator (demo user fmanager, badmin)</t>
+          <t>FIN_ADMIN – Comptrollership administrator (SIT/UAT user fmanager, badmin)</t>
         </is>
       </c>
       <c r="H73" s="12" t="inlineStr">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>FIN_ADMIN – Comptrollership administrator (demo user fmanager, badmin)</t>
+          <t>FIN_ADMIN – Comptrollership administrator (SIT/UAT user fmanager, badmin)</t>
         </is>
       </c>
       <c r="H74" s="12" t="inlineStr">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H75" s="12" t="inlineStr">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H77" s="12" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H78" s="12" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="M78" s="12" t="inlineStr">
         <is>
-          <t>DisbursementDemoIT#theApproverIsNeverTheProcessorAndOperationsKeepsItsBatchInReview</t>
+          <t>DisbursementSeedIT#theApproverIsNeverTheProcessorAndOperationsKeepsItsBatchInReview</t>
         </is>
       </c>
       <c r="N78" s="27" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H80" s="12" t="inlineStr">
@@ -15198,7 +15198,7 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H81" s="12" t="inlineStr">
@@ -15230,7 +15230,7 @@
       </c>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>DisbursementDemoIT#theApproverIsNeverTheProcessorAndOperationsKeepsItsBatchInReview</t>
+          <t>DisbursementSeedIT#theApproverIsNeverTheProcessorAndOperationsKeepsItsBatchInReview</t>
         </is>
       </c>
       <c r="N81" s="27" t="inlineStr">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H82" s="12" t="inlineStr">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H83" s="12" t="inlineStr">
@@ -15422,7 +15422,7 @@
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H84" s="12" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr">
@@ -15564,7 +15564,7 @@
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H86" s="12" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H87" s="12" t="inlineStr">
@@ -15701,7 +15701,7 @@
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H88" s="12" t="inlineStr">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H89" s="12" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H90" s="12" t="inlineStr">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H91" s="12" t="inlineStr">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H92" s="12" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H93" s="12" t="inlineStr">
@@ -16146,7 +16146,7 @@
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H94" s="12" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H95" s="12" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H96" s="12" t="inlineStr">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H97" s="12" t="inlineStr">
@@ -16429,7 +16429,7 @@
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H98" s="12" t="inlineStr">
@@ -16497,7 +16497,7 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
@@ -16566,7 +16566,7 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H100" s="12" t="inlineStr">
@@ -16635,7 +16635,7 @@
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H101" s="12" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H102" s="12" t="inlineStr">
@@ -16773,7 +16773,7 @@
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H103" s="12" t="inlineStr">
@@ -16849,7 +16849,7 @@
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H104" s="12" t="inlineStr">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H105" s="12" t="inlineStr">
@@ -16995,7 +16995,7 @@
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H106" s="12" t="inlineStr">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H107" s="12" t="inlineStr">
@@ -17147,7 +17147,7 @@
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H108" s="12" t="inlineStr">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H109" s="12" t="inlineStr">
@@ -17293,7 +17293,7 @@
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H110" s="12" t="inlineStr">
@@ -17369,7 +17369,7 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H111" s="12" t="inlineStr">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H112" s="12" t="inlineStr">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H113" s="12" t="inlineStr">
@@ -17578,7 +17578,7 @@
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H114" s="12" t="inlineStr">
@@ -17646,7 +17646,7 @@
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H115" s="12" t="inlineStr">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H116" s="12" t="inlineStr">
@@ -17786,7 +17786,7 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H117" s="12" t="inlineStr">
@@ -17854,7 +17854,7 @@
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H118" s="12" t="inlineStr">
@@ -17923,7 +17923,7 @@
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H119" s="12" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H120" s="12" t="inlineStr">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H121" s="12" t="inlineStr">
@@ -18136,7 +18136,7 @@
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H122" s="12" t="inlineStr">
@@ -18205,7 +18205,7 @@
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H123" s="12" t="inlineStr">
@@ -18274,7 +18274,7 @@
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H124" s="12" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H125" s="12" t="inlineStr">
@@ -18415,7 +18415,7 @@
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H126" s="12" t="inlineStr">
@@ -18488,7 +18488,7 @@
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H127" s="12" t="inlineStr">
@@ -18557,7 +18557,7 @@
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H128" s="12" t="inlineStr">
@@ -18629,7 +18629,7 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H129" s="12" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H130" s="12" t="inlineStr">
@@ -18770,7 +18770,7 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H131" s="12" t="inlineStr">
@@ -18838,7 +18838,7 @@
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H132" s="12" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H133" s="12" t="inlineStr">
@@ -18982,7 +18982,7 @@
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H134" s="12" t="inlineStr">
@@ -19050,7 +19050,7 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H135" s="12" t="inlineStr">
@@ -19119,7 +19119,7 @@
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H136" s="12" t="inlineStr">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
@@ -19259,7 +19259,7 @@
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H138" s="12" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H140" s="12" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
@@ -19543,7 +19543,7 @@
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="H142" s="12" t="inlineStr">
@@ -19612,7 +19612,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H143" s="12" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H144" s="12" t="inlineStr">
@@ -19753,7 +19753,7 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H145" s="12" t="inlineStr">
@@ -19822,7 +19822,7 @@
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H146" s="12" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H147" s="12" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H148" s="12" t="inlineStr">
@@ -20037,7 +20037,7 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H149" s="12" t="inlineStr">
@@ -20109,7 +20109,7 @@
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H150" s="12" t="inlineStr">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H151" s="12" t="inlineStr">
@@ -20246,7 +20246,7 @@
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H152" s="12" t="inlineStr">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H153" s="12" t="inlineStr">
@@ -20386,7 +20386,7 @@
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H154" s="12" t="inlineStr">
@@ -20458,7 +20458,7 @@
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H155" s="12" t="inlineStr">
@@ -20526,7 +20526,7 @@
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H156" s="12" t="inlineStr">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H157" s="12" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H158" s="12" t="inlineStr">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H159" s="12" t="inlineStr">
@@ -20814,7 +20814,7 @@
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H160" s="12" t="inlineStr">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H161" s="12" t="inlineStr">
@@ -20967,7 +20967,7 @@
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H162" s="12" t="inlineStr">
@@ -21040,7 +21040,7 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H163" s="12" t="inlineStr">
@@ -21116,7 +21116,7 @@
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H164" s="12" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H165" s="12" t="inlineStr">
@@ -21265,7 +21265,7 @@
       </c>
       <c r="G166" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H166" s="12" t="inlineStr">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H167" s="12" t="inlineStr">
@@ -21401,7 +21401,7 @@
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H168" s="12" t="inlineStr">
@@ -21473,7 +21473,7 @@
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H169" s="12" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
-          <t>PRQ_REVIEWER – Marketing Reviewer (demo user mktrev)</t>
+          <t>PRQ_REVIEWER – Marketing Reviewer (SIT/UAT user mktrev)</t>
         </is>
       </c>
       <c r="H170" s="12" t="inlineStr">
@@ -21617,7 +21617,7 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>PRQ_REVIEWER – Marketing Reviewer (demo user mktrev)</t>
+          <t>PRQ_REVIEWER – Marketing Reviewer (SIT/UAT user mktrev)</t>
         </is>
       </c>
       <c r="H171" s="12" t="inlineStr">
@@ -21693,7 +21693,7 @@
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
-          <t>PRQ_REVIEWER – Marketing Reviewer (demo user mktrev)</t>
+          <t>PRQ_REVIEWER – Marketing Reviewer (SIT/UAT user mktrev)</t>
         </is>
       </c>
       <c r="H172" s="12" t="inlineStr">
@@ -21767,7 +21767,7 @@
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="H173" s="12" t="inlineStr">
@@ -21839,7 +21839,7 @@
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H174" s="12" t="inlineStr">
@@ -21907,7 +21907,7 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H175" s="12" t="inlineStr">
@@ -21976,7 +21976,7 @@
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H176" s="12" t="inlineStr">
@@ -22053,7 +22053,7 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H177" s="12" t="inlineStr">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H178" s="12" t="inlineStr">
@@ -22203,7 +22203,7 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H179" s="12" t="inlineStr">
@@ -22276,7 +22276,7 @@
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H180" s="12" t="inlineStr">
@@ -22349,7 +22349,7 @@
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H181" s="12" t="inlineStr">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H182" s="12" t="inlineStr">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H183" s="12" t="inlineStr">
@@ -22568,7 +22568,7 @@
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H184" s="12" t="inlineStr">
@@ -22644,7 +22644,7 @@
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H185" s="12" t="inlineStr">
@@ -22721,7 +22721,7 @@
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H186" s="12" t="inlineStr">
@@ -22794,7 +22794,7 @@
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H187" s="12" t="inlineStr">
@@ -22867,7 +22867,7 @@
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
-          <t>PRQ_REVIEWER – Marketing Reviewer (demo user mktrev)</t>
+          <t>PRQ_REVIEWER – Marketing Reviewer (SIT/UAT user mktrev)</t>
         </is>
       </c>
       <c r="H188" s="12" t="inlineStr">
@@ -22943,7 +22943,7 @@
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
-          <t>PRQ_REVIEWER – Marketing Reviewer (demo user mktrev)</t>
+          <t>PRQ_REVIEWER – Marketing Reviewer (SIT/UAT user mktrev)</t>
         </is>
       </c>
       <c r="H189" s="12" t="inlineStr">
@@ -23012,7 +23012,7 @@
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
-          <t>PRQ_REVIEWER – Marketing Reviewer (demo user mktrev)</t>
+          <t>PRQ_REVIEWER – Marketing Reviewer (SIT/UAT user mktrev)</t>
         </is>
       </c>
       <c r="H190" s="12" t="inlineStr">
@@ -23080,7 +23080,7 @@
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
-          <t>PRQ_REVIEWER – Marketing Reviewer (demo user mktrev)</t>
+          <t>PRQ_REVIEWER – Marketing Reviewer (SIT/UAT user mktrev)</t>
         </is>
       </c>
       <c r="H191" s="12" t="inlineStr">
@@ -23149,7 +23149,7 @@
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H192" s="12" t="inlineStr">
@@ -23226,7 +23226,7 @@
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H193" s="12" t="inlineStr">
@@ -23303,7 +23303,7 @@
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="H194" s="12" t="inlineStr">
@@ -23379,7 +23379,7 @@
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="H195" s="12" t="inlineStr">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H196" s="12" t="inlineStr">
@@ -23525,7 +23525,7 @@
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H197" s="12" t="inlineStr">
@@ -23598,7 +23598,7 @@
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
-          <t>PRQ_REVIEWER – Marketing Reviewer (demo user mktrev)</t>
+          <t>PRQ_REVIEWER – Marketing Reviewer (SIT/UAT user mktrev)</t>
         </is>
       </c>
       <c r="H198" s="12" t="inlineStr">
@@ -23675,7 +23675,7 @@
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H199" s="12" t="inlineStr">
@@ -23753,7 +23753,7 @@
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H200" s="12" t="inlineStr">
@@ -23826,7 +23826,7 @@
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
-          <t>PRQ_REVIEWER – Marketing Reviewer (demo user mktrev)</t>
+          <t>PRQ_REVIEWER – Marketing Reviewer (SIT/UAT user mktrev)</t>
         </is>
       </c>
       <c r="H201" s="12" t="inlineStr">
@@ -23899,7 +23899,7 @@
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
-          <t>PRQ_APPROVER – Marketing Approver (demo user mktappr)</t>
+          <t>PRQ_APPROVER – Marketing Approver (SIT/UAT user mktappr)</t>
         </is>
       </c>
       <c r="H202" s="12" t="inlineStr">
@@ -23976,7 +23976,7 @@
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
-          <t>HR_APPROVER – HR Approver (demo user hrappr)</t>
+          <t>HR_APPROVER – HR Approver (SIT/UAT user hrappr)</t>
         </is>
       </c>
       <c r="H203" s="12" t="inlineStr">
@@ -24048,7 +24048,7 @@
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
-          <t>PRQ_APPROVER – Marketing Approver (demo user mktappr)</t>
+          <t>PRQ_APPROVER – Marketing Approver (SIT/UAT user mktappr)</t>
         </is>
       </c>
       <c r="H204" s="12" t="inlineStr">
@@ -24121,7 +24121,7 @@
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
-          <t>PRQ_APPROVER – Marketing Approver (demo user mktappr)</t>
+          <t>PRQ_APPROVER – Marketing Approver (SIT/UAT user mktappr)</t>
         </is>
       </c>
       <c r="H205" s="12" t="inlineStr">
@@ -24195,7 +24195,7 @@
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
-          <t>HR_APPROVER – HR Approver (demo user hrappr)</t>
+          <t>HR_APPROVER – HR Approver (SIT/UAT user hrappr)</t>
         </is>
       </c>
       <c r="H206" s="12" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H207" s="12" t="inlineStr">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H208" s="12" t="inlineStr">
@@ -24410,7 +24410,7 @@
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H209" s="12" t="inlineStr">
@@ -24478,7 +24478,7 @@
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H210" s="12" t="inlineStr">
@@ -24551,7 +24551,7 @@
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H211" s="12" t="inlineStr">
@@ -24620,7 +24620,7 @@
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H212" s="12" t="inlineStr">
@@ -24689,7 +24689,7 @@
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H213" s="12" t="inlineStr">
@@ -24758,7 +24758,7 @@
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H214" s="12" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H215" s="12" t="inlineStr">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H216" s="12" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H217" s="12" t="inlineStr">
@@ -25040,7 +25040,7 @@
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H218" s="12" t="inlineStr">
@@ -25112,7 +25112,7 @@
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H219" s="12" t="inlineStr">
@@ -25184,7 +25184,7 @@
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
-          <t>SYSTEM – BIBS scheduled job or event (demo user -)</t>
+          <t>SYSTEM – BIBS scheduled job or event (SIT/UAT user -)</t>
         </is>
       </c>
       <c r="H220" s="12" t="inlineStr">
@@ -25252,7 +25252,7 @@
       </c>
       <c r="G221" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H221" s="12" t="inlineStr">
@@ -25325,7 +25325,7 @@
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H222" s="12" t="inlineStr">
@@ -25393,7 +25393,7 @@
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H223" s="12" t="inlineStr">
@@ -25466,7 +25466,7 @@
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H224" s="12" t="inlineStr">
@@ -25538,7 +25538,7 @@
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="H225" s="12" t="inlineStr">
@@ -25610,7 +25610,7 @@
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H226" s="12" t="inlineStr">
@@ -25682,7 +25682,7 @@
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H227" s="12" t="inlineStr">
@@ -25755,7 +25755,7 @@
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H228" s="12" t="inlineStr">
@@ -25824,7 +25824,7 @@
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H229" s="12" t="inlineStr">
@@ -25901,7 +25901,7 @@
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
-          <t>PRQ_REVIEWER – Marketing Reviewer (demo user mktrev)</t>
+          <t>PRQ_REVIEWER – Marketing Reviewer (SIT/UAT user mktrev)</t>
         </is>
       </c>
       <c r="H230" s="12" t="inlineStr">
@@ -25977,7 +25977,7 @@
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H231" s="12" t="inlineStr">
@@ -26051,7 +26051,7 @@
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H232" s="12" t="inlineStr">
@@ -26128,7 +26128,7 @@
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H233" s="12" t="inlineStr">
@@ -26201,7 +26201,7 @@
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H234" s="12" t="inlineStr">
@@ -26278,7 +26278,7 @@
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H235" s="12" t="inlineStr">
@@ -26351,7 +26351,7 @@
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H236" s="12" t="inlineStr">
@@ -26424,7 +26424,7 @@
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
-          <t>PRQ_REVIEWER – Marketing Reviewer (demo user mktrev)</t>
+          <t>PRQ_REVIEWER – Marketing Reviewer (SIT/UAT user mktrev)</t>
         </is>
       </c>
       <c r="H237" s="12" t="inlineStr">
@@ -26498,7 +26498,7 @@
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="H238" s="12" t="inlineStr">
@@ -26571,7 +26571,7 @@
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H239" s="12" t="inlineStr">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H240" s="12" t="inlineStr">
@@ -26711,7 +26711,7 @@
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H241" s="12" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H242" s="12" t="inlineStr">
@@ -26857,7 +26857,7 @@
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H243" s="12" t="inlineStr">
@@ -26930,7 +26930,7 @@
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H244" s="12" t="inlineStr">
@@ -27007,7 +27007,7 @@
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H245" s="12" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H246" s="12" t="inlineStr">
@@ -27157,7 +27157,7 @@
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H247" s="12" t="inlineStr">
@@ -27230,7 +27230,7 @@
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H248" s="12" t="inlineStr">
@@ -27303,7 +27303,7 @@
       </c>
       <c r="G249" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H249" s="12" t="inlineStr">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H250" s="12" t="inlineStr">
@@ -27451,7 +27451,7 @@
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H251" s="12" t="inlineStr">
@@ -27523,7 +27523,7 @@
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H252" s="12" t="inlineStr">
@@ -27600,7 +27600,7 @@
       </c>
       <c r="G253" s="12" t="inlineStr">
         <is>
-          <t>ACSL_TL – ACSL Team Leader (demo user acsltl)</t>
+          <t>ACSL_TL – ACSL Team Leader (SIT/UAT user acsltl)</t>
         </is>
       </c>
       <c r="H253" s="12" t="inlineStr">
@@ -27673,7 +27673,7 @@
       </c>
       <c r="G254" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H254" s="12" t="inlineStr">
@@ -27745,7 +27745,7 @@
       </c>
       <c r="G255" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H255" s="12" t="inlineStr">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="G256" s="12" t="inlineStr">
         <is>
-          <t>ACSL_TL – ACSL Team Leader (demo user acsltl)</t>
+          <t>ACSL_TL – ACSL Team Leader (SIT/UAT user acsltl)</t>
         </is>
       </c>
       <c r="H256" s="12" t="inlineStr">
@@ -27886,7 +27886,7 @@
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H257" s="12" t="inlineStr">
@@ -27955,7 +27955,7 @@
       </c>
       <c r="G258" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H258" s="12" t="inlineStr">
@@ -28024,7 +28024,7 @@
       </c>
       <c r="G259" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H259" s="12" t="inlineStr">
@@ -28093,7 +28093,7 @@
       </c>
       <c r="G260" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H260" s="12" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="G261" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H261" s="12" t="inlineStr">
@@ -28233,7 +28233,7 @@
       </c>
       <c r="G262" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H262" s="12" t="inlineStr">
@@ -28302,7 +28302,7 @@
       </c>
       <c r="G263" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H263" s="12" t="inlineStr">
@@ -28375,7 +28375,7 @@
       </c>
       <c r="G264" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H264" s="12" t="inlineStr">
@@ -28444,7 +28444,7 @@
       </c>
       <c r="G265" s="12" t="inlineStr">
         <is>
-          <t>CASHIER – Cashier (demo user cashier, cashtl)</t>
+          <t>CASHIER – Cashier (SIT/UAT user cashier, cashtl)</t>
         </is>
       </c>
       <c r="H265" s="12" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="G266" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H266" s="12" t="inlineStr">
@@ -28585,7 +28585,7 @@
       </c>
       <c r="G267" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H267" s="12" t="inlineStr">
@@ -28654,7 +28654,7 @@
       </c>
       <c r="G268" s="12" t="inlineStr">
         <is>
-          <t>ACSL_TL – ACSL Team Leader (demo user acsltl)</t>
+          <t>ACSL_TL – ACSL Team Leader (SIT/UAT user acsltl)</t>
         </is>
       </c>
       <c r="H268" s="12" t="inlineStr">
@@ -28730,7 +28730,7 @@
       </c>
       <c r="G269" s="12" t="inlineStr">
         <is>
-          <t>ACSL_TL – ACSL Team Leader (demo user acsltl)</t>
+          <t>ACSL_TL – ACSL Team Leader (SIT/UAT user acsltl)</t>
         </is>
       </c>
       <c r="H269" s="12" t="inlineStr">
@@ -28799,7 +28799,7 @@
       </c>
       <c r="G270" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H270" s="12" t="inlineStr">
@@ -28871,7 +28871,7 @@
       </c>
       <c r="G271" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H271" s="12" t="inlineStr">
@@ -28943,7 +28943,7 @@
       </c>
       <c r="G272" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H272" s="12" t="inlineStr">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="G273" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H273" s="12" t="inlineStr">
@@ -29085,7 +29085,7 @@
       </c>
       <c r="G274" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H274" s="12" t="inlineStr">
@@ -29154,7 +29154,7 @@
       </c>
       <c r="G275" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H275" s="12" t="inlineStr">
@@ -29223,7 +29223,7 @@
       </c>
       <c r="G276" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H276" s="12" t="inlineStr">
@@ -29292,7 +29292,7 @@
       </c>
       <c r="G277" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H277" s="12" t="inlineStr">
@@ -29361,7 +29361,7 @@
       </c>
       <c r="G278" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H278" s="12" t="inlineStr">
@@ -29430,7 +29430,7 @@
       </c>
       <c r="G279" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H279" s="12" t="inlineStr">
@@ -29499,7 +29499,7 @@
       </c>
       <c r="G280" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H280" s="12" t="inlineStr">
@@ -29567,7 +29567,7 @@
       </c>
       <c r="G281" s="12" t="inlineStr">
         <is>
-          <t>ACSL_TL – ACSL Team Leader (demo user acsltl)</t>
+          <t>ACSL_TL – ACSL Team Leader (SIT/UAT user acsltl)</t>
         </is>
       </c>
       <c r="H281" s="12" t="inlineStr">
@@ -29639,7 +29639,7 @@
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
-          <t>ACSL_TL – ACSL Team Leader (demo user acsltl)</t>
+          <t>ACSL_TL – ACSL Team Leader (SIT/UAT user acsltl)</t>
         </is>
       </c>
       <c r="H282" s="12" t="inlineStr">
@@ -29711,7 +29711,7 @@
       </c>
       <c r="G283" s="12" t="inlineStr">
         <is>
-          <t>ACSL_TL – ACSL Team Leader (demo user acsltl)</t>
+          <t>ACSL_TL – ACSL Team Leader (SIT/UAT user acsltl)</t>
         </is>
       </c>
       <c r="H283" s="12" t="inlineStr">
@@ -29780,7 +29780,7 @@
       </c>
       <c r="G284" s="12" t="inlineStr">
         <is>
-          <t>ACSL_HEAD – ACSL Head (demo user acslhead)</t>
+          <t>ACSL_HEAD – ACSL Head (SIT/UAT user acslhead)</t>
         </is>
       </c>
       <c r="H284" s="12" t="inlineStr">
@@ -29852,7 +29852,7 @@
       </c>
       <c r="G285" s="12" t="inlineStr">
         <is>
-          <t>ACSL_HEAD – ACSL Head (demo user acslhead)</t>
+          <t>ACSL_HEAD – ACSL Head (SIT/UAT user acslhead)</t>
         </is>
       </c>
       <c r="H285" s="12" t="inlineStr">
@@ -29921,7 +29921,7 @@
       </c>
       <c r="G286" s="12" t="inlineStr">
         <is>
-          <t>ACSL_HEAD – ACSL Head (demo user acslhead)</t>
+          <t>ACSL_HEAD – ACSL Head (SIT/UAT user acslhead)</t>
         </is>
       </c>
       <c r="H286" s="12" t="inlineStr">
@@ -29994,7 +29994,7 @@
       </c>
       <c r="G287" s="12" t="inlineStr">
         <is>
-          <t>ACSL_HEAD – ACSL Head (demo user acslhead)</t>
+          <t>ACSL_HEAD – ACSL Head (SIT/UAT user acslhead)</t>
         </is>
       </c>
       <c r="H287" s="12" t="inlineStr">
@@ -30066,7 +30066,7 @@
       </c>
       <c r="G288" s="12" t="inlineStr">
         <is>
-          <t>ACSL_HEAD – ACSL Head (demo user acslhead)</t>
+          <t>ACSL_HEAD – ACSL Head (SIT/UAT user acslhead)</t>
         </is>
       </c>
       <c r="H288" s="12" t="inlineStr">
@@ -30139,7 +30139,7 @@
       </c>
       <c r="G289" s="12" t="inlineStr">
         <is>
-          <t>ACSL_HEAD – ACSL Head (demo user acslhead)</t>
+          <t>ACSL_HEAD – ACSL Head (SIT/UAT user acslhead)</t>
         </is>
       </c>
       <c r="H289" s="12" t="inlineStr">
@@ -30212,7 +30212,7 @@
       </c>
       <c r="G290" s="12" t="inlineStr">
         <is>
-          <t>ACSL_TL – ACSL Team Leader (demo user acsltl)</t>
+          <t>ACSL_TL – ACSL Team Leader (SIT/UAT user acsltl)</t>
         </is>
       </c>
       <c r="H290" s="12" t="inlineStr">
@@ -30288,7 +30288,7 @@
       </c>
       <c r="G291" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H291" s="12" t="inlineStr">
@@ -30364,7 +30364,7 @@
       </c>
       <c r="G292" s="12" t="inlineStr">
         <is>
-          <t>REMIT_TL – Remittance Team Lead (demo user remittl)</t>
+          <t>REMIT_TL – Remittance Team Lead (SIT/UAT user remittl)</t>
         </is>
       </c>
       <c r="H292" s="12" t="inlineStr">
@@ -30440,7 +30440,7 @@
       </c>
       <c r="G293" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H293" s="12" t="inlineStr">
@@ -30517,7 +30517,7 @@
       </c>
       <c r="G294" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H294" s="12" t="inlineStr">
@@ -30590,7 +30590,7 @@
       </c>
       <c r="G295" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H295" s="12" t="inlineStr">
@@ -30663,7 +30663,7 @@
       </c>
       <c r="G296" s="12" t="inlineStr">
         <is>
-          <t>ACSL_TL – ACSL Team Leader (demo user acsltl)</t>
+          <t>ACSL_TL – ACSL Team Leader (SIT/UAT user acsltl)</t>
         </is>
       </c>
       <c r="H296" s="12" t="inlineStr">
@@ -30736,7 +30736,7 @@
       </c>
       <c r="G297" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H297" s="12" t="inlineStr">
@@ -30808,7 +30808,7 @@
       </c>
       <c r="G298" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="H298" s="12" t="inlineStr">
@@ -41879,17 +41879,17 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Demo users and roles</t>
+          <t>SIT/UAT users and roles</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>disb (DISBURSEMENT), disbtl and disbtl2 (DISB_TL), disbappr and disbappr2 (DISB_APPROVER), mktao (PRQ_PROCESSOR), mktrev (PRQ_REVIEWER), mktappr (PRQ_APPROVER), hrappr (HR_APPROVER), acsl (ACSL_PROCESSOR), acsltl (ACSL_TL), acslhead (ACSL_HEAD), cashier and cashtl (CASHIER, CASHIER_TL), remittl (REMIT_TL), glofficer (FRBS_PROCESSOR), fmanager (FIN_ADMIN), badmin (BUSINESS_ADMIN), comptrol, admin, auditor. The demo password is issued by the test lead.</t>
+          <t>disb (DISBURSEMENT), disbtl and disbtl2 (DISB_TL), disbappr and disbappr2 (DISB_APPROVER), mktao (PRQ_PROCESSOR), mktrev (PRQ_REVIEWER), mktappr (PRQ_APPROVER), hrappr (HR_APPROVER), acsl (ACSL_PROCESSOR), acsltl (ACSL_TL), acslhead (ACSL_HEAD), cashier and cashtl (CASHIER, CASHIER_TL), remittl (REMIT_TL), glofficer (FRBS_PROCESSOR), fmanager (FIN_ADMIN), badmin (BUSINESS_ADMIN), comptrol, admin, auditor. The SIT/UAT password is issued by the test lead.</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Demo seeds V999 (BRD-5 users), V990, V980, V900; grants V890</t>
+          <t>Seeds V999 (BRD-5 users), V990, V980, V900; grants V890</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
@@ -41914,7 +41914,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Migrations V891-V893 and the demo runner DisbursementDemoData</t>
+          <t>Migrations V891-V893 and the seed runner DisbursementSeedData</t>
         </is>
       </c>
       <c r="E6" s="12" t="n">
@@ -41939,7 +41939,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Demo runner DisbursementDemoData (after the Operations runners)</t>
+          <t>Seed runner DisbursementSeedData (after the Operations runners)</t>
         </is>
       </c>
       <c r="E7" s="12" t="n">
@@ -41984,12 +41984,12 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>A refund request (RRF) of one client with two AR numbers of the cashiering demo, reason Overpayment, credit to account; a refund of a cancelled policy; a cash advance (RFP) for an employee with purpose and amount 5,000.00; documents (PDF and XLSX)</t>
+          <t>A refund request (RRF) of one client with two AR numbers of the cashiering seed, reason Overpayment, credit to account; a refund of a cancelled policy; a cash advance (RFP) for an employee with purpose and amount 5,000.00; documents (PDF and XLSX)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Keyed in by the tester (no Payment Requests demo storyline)</t>
+          <t>Keyed in by the tester (no Payment Requests seed storyline)</t>
         </is>
       </c>
       <c r="E9" s="12" t="n">
@@ -42014,7 +42014,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>SOA file prepared by the test lead; controls of V896-V897; demo runner DeductionDemoData</t>
+          <t>SOA file prepared by the test lead; controls of V896-V897; seed runner DeductionSeedData</t>
         </is>
       </c>
       <c r="E10" s="12" t="n">
@@ -42034,12 +42034,12 @@
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Remittance batches of the Operations demo; CPC2 incentive criterion (code CPC2, RATE basis) on packaged Motor lines; early-remittance incentive rules; EARLY_INCENTIVE_WTAX_RATE 2 %</t>
+          <t>Remittance batches of the Operations seed; CPC2 incentive criterion (code CPC2, RATE basis) on packaged Motor lines; early-remittance incentive rules; EARLY_INCENTIVE_WTAX_RATE 2 %</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Demo seeds V992, V996 and migration V772</t>
+          <t>Seeds V992, V996 and migration V772</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
@@ -42059,12 +42059,12 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>Demo employees with number, unit, branch and cost centre; the expense-role accounts of PRQ_CA_LIQUIDATION</t>
+          <t>Seed employees with number, unit, branch and cost centre; the expense-role accounts of PRQ_CA_LIQUIDATION</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Demo seed V999 and the Liquidation Accounts screen</t>
+          <t>Seed V999 and the Liquidation Accounts screen</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
@@ -42238,7 +42238,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -42289,7 +42289,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -42340,7 +42340,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -42391,7 +42391,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -42442,7 +42442,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -42493,7 +42493,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -42540,7 +42540,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -42587,7 +42587,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -42634,7 +42634,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -42681,7 +42681,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -42728,7 +42728,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -42775,7 +42775,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -42790,7 +42790,7 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>DisbursementDemoIT#theApproverIsNeverTheProcessorAndOperationsKeepsItsBatchInReview</t>
+          <t>DisbursementSeedIT#theApproverIsNeverTheProcessorAndOperationsKeepsItsBatchInReview</t>
         </is>
       </c>
       <c r="I16" s="27" t="inlineStr">
@@ -42826,7 +42826,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -42841,7 +42841,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>DisbursementDemoIT#theApproverIsNeverTheProcessorAndOperationsKeepsItsBatchInReview</t>
+          <t>DisbursementSeedIT#theApproverIsNeverTheProcessorAndOperationsKeepsItsBatchInReview</t>
         </is>
       </c>
       <c r="I17" s="27" t="inlineStr">
@@ -42877,7 +42877,7 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -42892,7 +42892,7 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>DisbursementDemoIT#theApproverIsNeverTheProcessorAndOperationsKeepsItsBatchInReview</t>
+          <t>DisbursementSeedIT#theApproverIsNeverTheProcessorAndOperationsKeepsItsBatchInReview</t>
         </is>
       </c>
       <c r="I18" s="27" t="inlineStr">
@@ -42928,7 +42928,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -42975,7 +42975,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -43022,7 +43022,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -43069,7 +43069,7 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -43120,7 +43120,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -43171,7 +43171,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -43222,7 +43222,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -43273,7 +43273,7 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -43324,7 +43324,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -43375,7 +43375,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -43422,7 +43422,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -43469,7 +43469,7 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -43516,7 +43516,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -43567,7 +43567,7 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -43618,7 +43618,7 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -43669,7 +43669,7 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -43720,7 +43720,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -43771,7 +43771,7 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>DISB_APPROVER – Disbursement Approver (demo user disbappr, disbappr2)</t>
+          <t>DISB_APPROVER – Disbursement Approver (SIT/UAT user disbappr, disbappr2)</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -43818,7 +43818,7 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -43865,7 +43865,7 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -43912,7 +43912,7 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -43963,7 +43963,7 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>PRQ_REVIEWER – Marketing Reviewer (demo user mktrev)</t>
+          <t>PRQ_REVIEWER – Marketing Reviewer (SIT/UAT user mktrev)</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -44014,7 +44014,7 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>PRQ_APPROVER – Marketing Approver (demo user mktappr)</t>
+          <t>PRQ_APPROVER – Marketing Approver (SIT/UAT user mktappr)</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -44065,7 +44065,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>HR_APPROVER – HR Approver (demo user hrappr)</t>
+          <t>HR_APPROVER – HR Approver (SIT/UAT user hrappr)</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -44116,7 +44116,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>DISBURSEMENT – Disbursement Processor (demo user disb)</t>
+          <t>DISBURSEMENT – Disbursement Processor (SIT/UAT user disb)</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -44167,7 +44167,7 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>PRQ_REVIEWER – Marketing Reviewer (demo user mktrev)</t>
+          <t>PRQ_REVIEWER – Marketing Reviewer (SIT/UAT user mktrev)</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -44218,7 +44218,7 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -44269,7 +44269,7 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>PRQ_APPROVER – Marketing Approver (demo user mktappr)</t>
+          <t>PRQ_APPROVER – Marketing Approver (SIT/UAT user mktappr)</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -44320,7 +44320,7 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>HR_APPROVER – HR Approver (demo user hrappr)</t>
+          <t>HR_APPROVER – HR Approver (SIT/UAT user hrappr)</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -44371,7 +44371,7 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>PRQ_APPROVER – Marketing Approver (demo user mktappr)</t>
+          <t>PRQ_APPROVER – Marketing Approver (SIT/UAT user mktappr)</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -44418,7 +44418,7 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -44465,7 +44465,7 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>PRQ_REVIEWER – Marketing Reviewer (demo user mktrev)</t>
+          <t>PRQ_REVIEWER – Marketing Reviewer (SIT/UAT user mktrev)</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -44512,7 +44512,7 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>HR_APPROVER – HR Approver (demo user hrappr)</t>
+          <t>HR_APPROVER – HR Approver (SIT/UAT user hrappr)</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -44559,7 +44559,7 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>HR_APPROVER – HR Approver (demo user hrappr)</t>
+          <t>HR_APPROVER – HR Approver (SIT/UAT user hrappr)</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -44610,7 +44610,7 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>PRQ_APPROVER – Marketing Approver (demo user mktappr)</t>
+          <t>PRQ_APPROVER – Marketing Approver (SIT/UAT user mktappr)</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -44661,7 +44661,7 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -44712,7 +44712,7 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>ACSL_TL – ACSL Team Leader (demo user acsltl)</t>
+          <t>ACSL_TL – ACSL Team Leader (SIT/UAT user acsltl)</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -44763,7 +44763,7 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>ACSL_HEAD – ACSL Head (demo user acslhead)</t>
+          <t>ACSL_HEAD – ACSL Head (SIT/UAT user acslhead)</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -44814,7 +44814,7 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -44865,7 +44865,7 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>ACSL_TL – ACSL Team Leader (demo user acsltl)</t>
+          <t>ACSL_TL – ACSL Team Leader (SIT/UAT user acsltl)</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -44916,7 +44916,7 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -44967,7 +44967,7 @@
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>ACSL_HEAD – ACSL Head (demo user acslhead)</t>
+          <t>ACSL_HEAD – ACSL Head (SIT/UAT user acslhead)</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
@@ -45018,7 +45018,7 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>ACSL_HEAD – ACSL Head (demo user acslhead)</t>
+          <t>ACSL_HEAD – ACSL Head (SIT/UAT user acslhead)</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -45069,7 +45069,7 @@
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>ACSL_TL – ACSL Team Leader (demo user acsltl)</t>
+          <t>ACSL_TL – ACSL Team Leader (SIT/UAT user acsltl)</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
@@ -45120,7 +45120,7 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -45171,7 +45171,7 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>ACSL_TL – ACSL Team Leader (demo user acsltl)</t>
+          <t>ACSL_TL – ACSL Team Leader (SIT/UAT user acsltl)</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
@@ -45218,7 +45218,7 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>ACSL_PROCESSOR – ACSL Processor (demo user acsl)</t>
+          <t>ACSL_PROCESSOR – ACSL Processor (SIT/UAT user acsl)</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -45265,7 +45265,7 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>ACSL_HEAD – ACSL Head (demo user acslhead)</t>
+          <t>ACSL_HEAD – ACSL Head (SIT/UAT user acslhead)</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
@@ -45312,7 +45312,7 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -45359,7 +45359,7 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>AUDITOR – Auditor (demo user auditor)</t>
+          <t>AUDITOR – Auditor (SIT/UAT user auditor)</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -45406,7 +45406,7 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>PRQ_PROCESSOR – Marketing Processor (AO) (demo user mktao)</t>
+          <t>PRQ_PROCESSOR – Marketing Processor (AO) (SIT/UAT user mktao)</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -45453,7 +45453,7 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>HR_APPROVER – HR Approver (demo user hrappr)</t>
+          <t>HR_APPROVER – HR Approver (SIT/UAT user hrappr)</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -45500,7 +45500,7 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>FIN_ADMIN – Comptrollership administrator (demo user fmanager, badmin)</t>
+          <t>FIN_ADMIN – Comptrollership administrator (SIT/UAT user fmanager, badmin)</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -45551,7 +45551,7 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>DISB_TL – Disbursement Team Leader (demo user disbtl, disbtl2)</t>
+          <t>DISB_TL – Disbursement Team Leader (SIT/UAT user disbtl, disbtl2)</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -45602,7 +45602,7 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>COMPTROLLERSHIP – Comptrollership (demo user comptrol)</t>
+          <t>COMPTROLLERSHIP – Comptrollership (SIT/UAT user comptrol)</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
